--- a/behavioral_rawdata.xlsx
+++ b/behavioral_rawdata.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\u_backup\近红外冥想项目\Study2\results V2\Psychophysiology\Data and Code\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\u_backup\近红外冥想项目\Study2\results V2\Acta Psychologica\Revision 1st\Data and Code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA202137-2EE1-4A10-907B-3B812965CDF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC9AB174-B8A6-422A-B7E0-EC2CC07E852E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5040" yWindow="2678" windowWidth="21600" windowHeight="11324" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6600" yWindow="1845" windowWidth="21600" windowHeight="11175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="pretest" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="41">
   <si>
     <t>SubjectNumber</t>
   </si>
@@ -178,6 +178,16 @@
   <si>
     <t>PropE_LongSaving</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Condition</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PE</t>
+  </si>
+  <si>
+    <t>EP</t>
   </si>
 </sst>
 </file>
@@ -534,23 +544,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L41"/>
-  <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:M41"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19.9296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.06640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.9296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.53125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="91.53125" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.73046875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.796875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="20.19921875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="19.796875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="39.53125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="91.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.75" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.75" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20.25" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19.75" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="39.5" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -587,8 +598,11 @@
       <c r="L1" s="2" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M1" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -623,8 +637,11 @@
       <c r="L2" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -659,8 +676,11 @@
       <c r="L3" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -695,8 +715,11 @@
       <c r="L4" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -731,8 +754,11 @@
       <c r="L5" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -767,8 +793,11 @@
       <c r="L6" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -803,8 +832,11 @@
       <c r="L7" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M7" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -839,8 +871,11 @@
       <c r="L8" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -875,8 +910,11 @@
       <c r="L9" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M9" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -911,8 +949,11 @@
       <c r="L10" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M10" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -947,8 +988,11 @@
       <c r="L11" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M11" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -983,8 +1027,11 @@
       <c r="L12" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M12" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -1021,8 +1068,11 @@
       <c r="L13" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -1057,8 +1107,11 @@
       <c r="L14" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M14" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -1093,8 +1146,11 @@
       <c r="L15" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M15" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -1131,8 +1187,11 @@
       <c r="L16">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M16" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -1167,8 +1226,11 @@
       <c r="L17" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M17" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -1203,8 +1265,11 @@
       <c r="L18" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M18" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -1241,8 +1306,11 @@
       <c r="L19" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M19" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
         <v>19</v>
       </c>
@@ -1277,8 +1345,11 @@
       <c r="L20" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M20" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
         <v>20</v>
       </c>
@@ -1313,8 +1384,11 @@
       <c r="L21" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M21" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
         <v>21</v>
       </c>
@@ -1351,8 +1425,11 @@
       <c r="L22" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M22" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
         <v>22</v>
       </c>
@@ -1389,8 +1466,11 @@
       <c r="L23" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M23" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
         <v>23</v>
       </c>
@@ -1425,8 +1505,11 @@
       <c r="L24" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M24" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
         <v>24</v>
       </c>
@@ -1463,8 +1546,11 @@
       <c r="L25" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M25" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
         <v>25</v>
       </c>
@@ -1501,8 +1587,11 @@
       <c r="L26" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
         <v>26</v>
       </c>
@@ -1537,8 +1626,11 @@
       <c r="L27" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M27" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
         <v>27</v>
       </c>
@@ -1575,8 +1667,11 @@
       <c r="L28" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M28" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
         <v>28</v>
       </c>
@@ -1613,8 +1708,11 @@
       <c r="L29" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M29" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
         <v>29</v>
       </c>
@@ -1651,8 +1749,11 @@
       <c r="L30" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M30" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
         <v>30</v>
       </c>
@@ -1687,8 +1788,11 @@
       <c r="L31" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M31" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A32" s="1">
         <v>31</v>
       </c>
@@ -1723,8 +1827,11 @@
       <c r="L32" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M32" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A33" s="1">
         <v>32</v>
       </c>
@@ -1759,8 +1866,11 @@
       <c r="L33" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M33" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>33</v>
       </c>
@@ -1791,8 +1901,11 @@
       <c r="L34" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M34" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A35" s="1">
         <v>34</v>
       </c>
@@ -1827,8 +1940,11 @@
       <c r="L35" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M35" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A36" s="1">
         <v>35</v>
       </c>
@@ -1863,8 +1979,11 @@
       <c r="L36" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M36" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A37" s="1">
         <v>36</v>
       </c>
@@ -1899,8 +2018,11 @@
       <c r="L37" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M37" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A38" s="1">
         <v>37</v>
       </c>
@@ -1935,8 +2057,11 @@
       <c r="L38" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M38" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A39" s="1">
         <v>38</v>
       </c>
@@ -1971,8 +2096,11 @@
       <c r="L39" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M39" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A40" s="1">
         <v>39</v>
       </c>
@@ -2007,8 +2135,11 @@
       <c r="L40" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M40" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A41" s="1">
         <v>40</v>
       </c>
@@ -2042,6 +2173,9 @@
       </c>
       <c r="L41" s="1">
         <v>0</v>
+      </c>
+      <c r="M41" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -2055,29 +2189,29 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F51745C-900E-4301-9C69-D43452BBCE41}">
   <dimension ref="A1:R41"/>
-  <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19.9296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.06640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.9296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.53125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.1328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.86328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.875" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="16" customWidth="1"/>
-    <col min="9" max="9" width="23.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="23.46484375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23.375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="23.5" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="23" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.6640625" customWidth="1"/>
-    <col min="13" max="14" width="15.73046875" customWidth="1"/>
-    <col min="15" max="15" width="23.06640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="23.33203125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="22.86328125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="39.53125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="22.6640625" customWidth="1"/>
-    <col min="20" max="20" width="18.3984375" customWidth="1"/>
+    <col min="12" max="12" width="18.625" customWidth="1"/>
+    <col min="13" max="14" width="15.75" customWidth="1"/>
+    <col min="15" max="15" width="23.125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="23.375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="22.875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="39.5" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="22.625" customWidth="1"/>
+    <col min="20" max="20" width="18.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="3" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:18" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2133,7 +2267,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -2189,7 +2323,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -2245,7 +2379,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -2301,7 +2435,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -2357,7 +2491,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -2413,7 +2547,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -2469,7 +2603,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -2525,7 +2659,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -2581,7 +2715,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -2637,7 +2771,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -2693,7 +2827,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -2749,7 +2883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -2805,7 +2939,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -2861,7 +2995,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -2917,7 +3051,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>15</v>
       </c>
@@ -2970,7 +3104,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -3026,7 +3160,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -3082,7 +3216,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -3138,7 +3272,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
         <v>19</v>
       </c>
@@ -3194,7 +3328,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
         <v>20</v>
       </c>
@@ -3250,7 +3384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
         <v>21</v>
       </c>
@@ -3306,7 +3440,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
         <v>22</v>
       </c>
@@ -3362,7 +3496,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
         <v>23</v>
       </c>
@@ -3418,7 +3552,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
         <v>24</v>
       </c>
@@ -3474,7 +3608,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
         <v>25</v>
       </c>
@@ -3530,7 +3664,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
         <v>26</v>
       </c>
@@ -3586,7 +3720,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
         <v>27</v>
       </c>
@@ -3642,7 +3776,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
         <v>28</v>
       </c>
@@ -3698,7 +3832,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
         <v>29</v>
       </c>
@@ -3754,7 +3888,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
         <v>30</v>
       </c>
@@ -3810,7 +3944,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A32" s="1">
         <v>31</v>
       </c>
@@ -3866,7 +4000,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A33" s="1">
         <v>32</v>
       </c>
@@ -3922,7 +4056,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A34" s="1">
         <v>33</v>
       </c>
@@ -3978,7 +4112,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A35" s="1">
         <v>34</v>
       </c>
@@ -4034,7 +4168,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A36" s="1">
         <v>35</v>
       </c>
@@ -4090,7 +4224,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A37" s="1">
         <v>36</v>
       </c>
@@ -4146,7 +4280,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A38" s="1">
         <v>37</v>
       </c>
@@ -4202,7 +4336,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A39" s="1">
         <v>38</v>
       </c>
@@ -4258,7 +4392,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:18" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:18" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A40" s="1">
         <v>39</v>
       </c>
@@ -4314,7 +4448,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A41" s="1">
         <v>40</v>
       </c>
@@ -4380,15 +4514,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8A137B0-2668-4E18-B1E4-B7FDB9A3F9B4}">
   <dimension ref="A1:E39"/>
-  <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.3984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.3984375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.3984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -4405,7 +4539,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -4422,7 +4556,7 @@
         <v>8.0179296102222074E-4</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>3</v>
       </c>
@@ -4439,7 +4573,7 @@
         <v>1.1267072334953922E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>4</v>
       </c>
@@ -4456,7 +4590,7 @@
         <v>8.0179296102222074E-4</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>6</v>
       </c>
@@ -4473,7 +4607,7 @@
         <v>8.0179296102222074E-4</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>7</v>
       </c>
@@ -4490,7 +4624,7 @@
         <v>8.2347180430027253E-4</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>8</v>
       </c>
@@ -4507,7 +4641,7 @@
         <v>3.2246786488588385E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>9</v>
       </c>
@@ -4524,7 +4658,7 @@
         <v>1.2850623299116128E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>10</v>
       </c>
@@ -4541,7 +4675,7 @@
         <v>3.2246786488588385E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>11</v>
       </c>
@@ -4558,7 +4692,7 @@
         <v>1.1774933392840886E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>12</v>
       </c>
@@ -4575,7 +4709,7 @@
         <v>3.2246786488588385E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>13</v>
       </c>
@@ -4592,7 +4726,7 @@
         <v>8.2347180430027253E-4</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>14</v>
       </c>
@@ -4609,7 +4743,7 @@
         <v>3.2246786488588385E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>15</v>
       </c>
@@ -4626,7 +4760,7 @@
         <v>1.1267072334953922E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>16</v>
       </c>
@@ -4643,7 +4777,7 @@
         <v>1.2850623299116128E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>17</v>
       </c>
@@ -4660,7 +4794,7 @@
         <v>1.2850623299116128E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>18</v>
       </c>
@@ -4677,7 +4811,7 @@
         <v>8.2347180430027253E-4</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>19</v>
       </c>
@@ -4694,7 +4828,7 @@
         <v>1.2850623299116128E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>20</v>
       </c>
@@ -4711,7 +4845,7 @@
         <v>3.2246786488588385E-3</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>21</v>
       </c>
@@ -4728,7 +4862,7 @@
         <v>4.0031683091896098E-4</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>22</v>
       </c>
@@ -4745,7 +4879,7 @@
         <v>1.2850623299116128E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>23</v>
       </c>
@@ -4762,7 +4896,7 @@
         <v>8.0179296102222074E-4</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>24</v>
       </c>
@@ -4779,7 +4913,7 @@
         <v>8.0179296102222074E-4</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>25</v>
       </c>
@@ -4796,7 +4930,7 @@
         <v>3.380505855197437E-3</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>26</v>
       </c>
@@ -4813,7 +4947,7 @@
         <v>1.2850623299116128E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>27</v>
       </c>
@@ -4830,7 +4964,7 @@
         <v>3.881270856834506E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>28</v>
       </c>
@@ -4847,7 +4981,7 @@
         <v>8.0179296102222074E-4</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>29</v>
       </c>
@@ -4864,7 +4998,7 @@
         <v>0.22514716129596513</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>30</v>
       </c>
@@ -4881,7 +5015,7 @@
         <v>1.616236509079655E-4</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>31</v>
       </c>
@@ -4898,7 +5032,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>32</v>
       </c>
@@ -4915,7 +5049,7 @@
         <v>8.6344396804104672E-4</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>33</v>
       </c>
@@ -4932,7 +5066,7 @@
         <v>3.3193603920945759E-3</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>34</v>
       </c>
@@ -4949,7 +5083,7 @@
         <v>8.2347180430027253E-4</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>35</v>
       </c>
@@ -4966,7 +5100,7 @@
         <v>1.1267072334953922E-2</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>36</v>
       </c>
@@ -4983,7 +5117,7 @@
         <v>3.3193603920945759E-3</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>37</v>
       </c>
@@ -5000,7 +5134,7 @@
         <v>8.0179296102222074E-4</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>38</v>
       </c>
@@ -5017,7 +5151,7 @@
         <v>8.6344396804104672E-4</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>39</v>
       </c>
@@ -5034,7 +5168,7 @@
         <v>1.1774933392840886E-2</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>40</v>
       </c>
